--- a/test_automation_framework/configs/test_cases.xlsx
+++ b/test_automation_framework/configs/test_cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/PycharmProjects/test_automation_framework_ws/configs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/PycharmProjects/etl_automation_jan/test_automation_framework/configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C11468-97B3-1942-901E-094451AE0CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB841F89-1AFC-C344-A702-21EA0F78C048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="740" windowWidth="28800" windowHeight="16020" xr2:uid="{65144EEF-1F90-C947-8815-970505B648B2}"/>
+    <workbookView xWindow="-28800" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{65144EEF-1F90-C947-8815-970505B648B2}"/>
   </bookViews>
   <sheets>
     <sheet name="test_cases" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -47,9 +47,6 @@
     <t>target_path</t>
   </si>
   <si>
-    <t>null_columns</t>
-  </si>
-  <si>
     <t>source_type</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>city</t>
-  </si>
-  <si>
     <t>min_val</t>
   </si>
   <si>
@@ -80,18 +74,12 @@
     <t>dq_col</t>
   </si>
   <si>
-    <t>result_margin</t>
-  </si>
-  <si>
     <t>source_query</t>
   </si>
   <si>
     <t>NA</t>
   </si>
   <si>
-    <t>parquet</t>
-  </si>
-  <si>
     <t>target_query</t>
   </si>
   <si>
@@ -104,10 +92,46 @@
     <t>count</t>
   </si>
   <si>
-    <t>/Users/admin/PycharmProjects/test_automation_framework_ws/input_files/Contact_info.csv</t>
-  </si>
-  <si>
-    <t>/Users/admin/PycharmProjects/test_automation_framework_ws/input_files/userdata1.parquet</t>
+    <t>/Users/admin/PycharmProjects/etl_automation_jan/test_automation_framework/input_files/sample_csv_source.csv</t>
+  </si>
+  <si>
+    <t>/Users/admin/PycharmProjects/etl_automation_jan/test_automation_framework/input_files/sample_csv_target.csv</t>
+  </si>
+  <si>
+    <t>id,name</t>
+  </si>
+  <si>
+    <t>not_null_columns</t>
+  </si>
+  <si>
+    <t>unique_columns</t>
+  </si>
+  <si>
+    <t>id,loc</t>
+  </si>
+  <si>
+    <t>paruet</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>count,duplicate,null,unique,data_compare</t>
+  </si>
+  <si>
+    <t>file_header</t>
+  </si>
+  <si>
+    <t>file_separator</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>|</t>
   </si>
 </sst>
 </file>
@@ -486,115 +510,204 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{713BC9B6-5492-CA4F-A877-3577F5CB424B}">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="80.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="82.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="82.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="80.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="82.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="82.33203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26" customWidth="1"/>
+    <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="36.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="Q2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="N1" t="s">
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
         <v>20</v>
       </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2">
-        <v>100</v>
-      </c>
-      <c r="K2">
-        <v>200</v>
-      </c>
-      <c r="L2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="H5" s="1"/>
+    <row r="5" spans="1:17">
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test_automation_framework/configs/test_cases.xlsx
+++ b/test_automation_framework/configs/test_cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/PycharmProjects/etl_automation_jan/test_automation_framework/configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB841F89-1AFC-C344-A702-21EA0F78C048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37103848-D59D-0644-BF09-E537ADD05E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28800" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{65144EEF-1F90-C947-8815-970505B648B2}"/>
+    <workbookView xWindow="-33600" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{65144EEF-1F90-C947-8815-970505B648B2}"/>
   </bookViews>
   <sheets>
     <sheet name="test_cases" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>id</t>
   </si>
@@ -89,9 +89,6 @@
     <t>validations</t>
   </si>
   <si>
-    <t>count</t>
-  </si>
-  <si>
     <t>/Users/admin/PycharmProjects/etl_automation_jan/test_automation_framework/input_files/sample_csv_source.csv</t>
   </si>
   <si>
@@ -110,35 +107,67 @@
     <t>id,loc</t>
   </si>
   <si>
-    <t>paruet</t>
-  </si>
-  <si>
-    <t>json</t>
+    <t>file_header</t>
+  </si>
+  <si>
+    <t>file_separator</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>parquet</t>
+  </si>
+  <si>
+    <t>/Users/admin/PycharmProjects/etl_automation_jan/test_automation_framework/input_files/userdata1.parquet</t>
+  </si>
+  <si>
+    <t>SELECT
+  *
+FROM
+  "CONTACT"."PUBLIC"."CONTACT_INFO"</t>
+  </si>
+  <si>
+    <t>IDENTIFIER</t>
+  </si>
+  <si>
+    <t>SURNAME</t>
+  </si>
+  <si>
+    <t>snowflake_qa</t>
+  </si>
+  <si>
+    <t>database</t>
+  </si>
+  <si>
+    <t>count,duplicate,data_compare</t>
+  </si>
+  <si>
+    <t>count,data_compare</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>count,duplicate,null,unique,data_compare</t>
-  </si>
-  <si>
-    <t>file_header</t>
-  </si>
-  <si>
-    <t>file_separator</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>|</t>
+    <t>SELECT
+  *
+FROM
+  "CONTACT"."PUBLIC"."CONTACT_INFO_T"</t>
+  </si>
+  <si>
+    <t>SELECT
+    identifier,
+    UPPER(surname) AS surname,
+    UPPER(given_name) AS given_name
+FROM
+    "CONTACT"."PUBLIC"."CONTACT_INFO" where identifier = 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -149,6 +178,12 @@
     <font>
       <sz val="11.3"/>
       <color theme="1"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12.8"/>
+      <color rgb="FF067D17"/>
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
@@ -173,9 +208,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,10 +576,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -558,10 +597,10 @@
         <v>6</v>
       </c>
       <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
         <v>21</v>
-      </c>
-      <c r="K1" t="s">
-        <v>22</v>
       </c>
       <c r="L1" t="s">
         <v>7</v>
@@ -587,13 +626,13 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -602,7 +641,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
@@ -611,98 +650,104 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="68">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
       <c r="Q3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" ht="102">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
       </c>
       <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
       <c r="Q4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:17">
